--- a/customer_service_import_template.xlsx
+++ b/customer_service_import_template.xlsx
@@ -494,12 +494,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>七天无理由</t>
+          <t>退换货政策</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>本店支持7天无理由退换，商品不影响二次销售即可申请，退款将原路退回。</t>
+          <t>本店为剪裁面料类商品，不支持7天无理由退换货（面料一经剪裁影响二次销售）。仅接受质量问题、错发或漏发的退换，需提供清晰照片凭证并在签收后48小时内联系客服处理。</t>
         </is>
       </c>
     </row>
@@ -531,7 +531,6 @@
           <t>支付</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>优惠券</t>

--- a/customer_service_import_template.xlsx
+++ b/customer_service_import_template.xlsx
@@ -1,33 +1,43 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="768" yWindow="768" windowWidth="23040" windowHeight="12120" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="客服知识" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="客服知识" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <family val="3"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <family val="3"/>
+      <sz val="9"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -39,7 +49,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="004472C4"/>
+        <fgColor rgb="FF4472C4"/>
       </patternFill>
     </fill>
   </fills>
@@ -65,7 +75,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -428,11 +438,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="1" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
   </cols>
@@ -481,7 +490,7 @@
         </is>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="43.2" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
           <t>售后</t>
@@ -499,11 +508,11 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>本店为剪裁面料类商品，不支持7天无理由退换货（面料一经剪裁影响二次销售）。仅接受质量问题、错发或漏发的退换，需提供清晰照片凭证并在签收后48小时内联系客服处理。</t>
+          <t>本店均为剪裁面料类商品，均不支持7天无理由退换货（面料一经剪裁影响二次销售）。仅接受质量问题、错发或漏发的退换，需提供清晰照片凭证并在签收后48小时内联系客服处理。</t>
         </is>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="28.8" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
           <t>物流</t>
@@ -539,6 +548,28 @@
       <c r="D5" s="2" t="inlineStr">
         <is>
           <t>店铺优惠券在结算时自动抵扣，具体以商品详情页说明为准。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>服务</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>裁剪</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>按米裁剪</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>亲，本店面料支持按米裁剪，您下单时在订单备注里写清楚需要的米数即可（例如“裁 2.5 米”）。默认多拍连裁：您拍几件我们就把布料连成整段一起裁切，保证是一整段、不拼接。如果有指定的裁切尺寸、拼色或其他要求，也请在备注里一并说明，我们会按您的要求处理。</t>
         </is>
       </c>
     </row>

--- a/customer_service_import_template.xlsx
+++ b/customer_service_import_template.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="2"/>
@@ -569,7 +569,24 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>亲，本店面料支持按米裁剪，您下单时在订单备注里写清楚需要的米数即可（例如“裁 2.5 米”）。默认多拍连裁：您拍几件我们就把布料连成整段一起裁切，保证是一整段、不拼接。如果有指定的裁切尺寸、拼色或其他要求，也请在备注里一并说明，我们会按您的要求处理。</t>
+          <t>亲，本店面料支持按米裁剪，您下单时在订单备注里写清楚需要的米数即可（例如“裁 2.5 米”）。默认多拍连裁：您拍几件我们就把布料连成整段一起裁切，保证是一整段如果有指定的裁切尺寸、拼色或其他要求，也请在备注里一并说明，我们会按您的要求处理。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>售后</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>无赠送活动</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>亲，本店目前没有任何赠送或优惠活动哦。不管买多少米都不送，没有买几送几、满减、折扣之类的促销。价格就是商品标价，按实际购买数量计费，不搞任何套路。</t>
         </is>
       </c>
     </row>

--- a/customer_service_import_template.xlsx
+++ b/customer_service_import_template.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="2"/>
@@ -590,6 +590,28 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>服务</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>质量</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>裁剪(剪裁)质量</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>亲，本店裁剪（也常写剪裁）质量您放心。每米面料出厂前都经过验布和质检，裁切边缘平整、不毛边、尺寸精准，按您备注的米数连成整段一起裁，不拼接。如果您收到的裁剪质量不满意（如毛边、尺寸偏差），拍清晰照片联系客服，我们核实后给您处理或补发。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/customer_service_import_template.xlsx
+++ b/customer_service_import_template.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="768" yWindow="768" windowWidth="23040" windowHeight="12120" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="390" yWindow="390" windowWidth="19200" windowHeight="11210" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="客服知识" sheetId="1" state="visible" r:id="rId1"/>
@@ -438,8 +438,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <dimension ref="A1:D9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
@@ -490,7 +490,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="43.2" customHeight="1">
+    <row r="3" ht="43.25" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
           <t>售后</t>
@@ -512,7 +512,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="28.8" customHeight="1">
+    <row r="4" ht="28.75" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
           <t>物流</t>
@@ -569,7 +569,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>亲，本店面料支持按米裁剪，您下单时在订单备注里写清楚需要的米数即可（例如“裁 2.5 米”）。默认多拍连裁：您拍几件我们就把布料连成整段一起裁切，保证是一整段如果有指定的裁切尺寸、拼色或其他要求，也请在备注里一并说明，我们会按您的要求处理。</t>
+          <t>亲，本店面料支持按米裁剪哦。您下单时在订单备注里写清楚需要的米数即可（例如"裁2.5米"）。默认多拍连裁：您拍几件我们就把布料连成整段一起裁切，保证是一整段。如果对长度有特殊要求也可以在备注里说明哦。</t>
         </is>
       </c>
     </row>
@@ -608,7 +608,29 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>亲，本店裁剪（也常写剪裁）质量您放心。每米面料出厂前都经过验布和质检，裁切边缘平整、不毛边、尺寸精准，按您备注的米数连成整段一起裁，不拼接。如果您收到的裁剪质量不满意（如毛边、尺寸偏差），拍清晰照片联系客服，我们核实后给您处理或补发。</t>
+          <t>亲，本店裁剪（也常写剪裁）质量您放心哦。每米面料出厂前都经过验布和质检，裁切边缘平整、不毛边、尺寸精准，按您备注的米数连成整段一起裁。如果您收到的裁剪质量不满意（如毛边、尺寸偏差），拍清晰照片联系客服，我们核实后给您处理或补发。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>服务</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>规格</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>面料宽度/幅宽</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>亲，我们面料的幅宽是固定的哦（一般在1.41~1.45米之间），店铺不支持自选宽度或修改宽度呢。如果您需要的宽度和我们幅宽不一样，建议您买回去自己裁一下就好啦，面料本身是可以正常裁切的。只有长度可以按您的需求备注特殊要求哦，宽度没办法改的。</t>
         </is>
       </c>
     </row>

--- a/customer_service_import_template.xlsx
+++ b/customer_service_import_template.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="390" yWindow="390" windowWidth="19200" windowHeight="11210" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="1584" yWindow="1584" windowWidth="23040" windowHeight="12120" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="客服知识" sheetId="1" state="visible" r:id="rId1"/>
@@ -438,8 +438,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
@@ -490,7 +490,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="43.25" customHeight="1">
+    <row r="3" ht="43.2" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
           <t>售后</t>
@@ -512,7 +512,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="28.75" customHeight="1">
+    <row r="4" ht="28.8" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
           <t>物流</t>
@@ -630,7 +630,29 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>亲，我们面料的幅宽是固定的哦（一般在1.41~1.45米之间），店铺不支持自选宽度或修改宽度呢。如果您需要的宽度和我们幅宽不一样，建议您买回去自己裁一下就好啦，面料本身是可以正常裁切的。只有长度可以按您的需求备注特殊要求哦，宽度没办法改的。</t>
+          <t>亲，我们面料的幅宽是1.41~1.45米之间哦。不同批次可能会有一点点浮动，但基本都在这个范围呢。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>服务</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>规格</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>宽度能否修改/自选</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>亲，店铺不支持自选宽度或修改宽度哦。我们面料的幅宽是固定的，没办法按您的要求改宽度呢。如果您需要的宽度和我们不一样，建议买回去自己裁一下就好啦，面料本身是可以正常裁切的。</t>
         </is>
       </c>
     </row>

--- a/customer_service_import_template.xlsx
+++ b/customer_service_import_template.xlsx
@@ -652,7 +652,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>亲，店铺不支持自选宽度或修改宽度哦。我们面料的幅宽是固定的，没办法按您的要求改宽度呢。如果您需要的宽度和我们不一样，建议买回去自己裁一下就好啦，面料本身是可以正常裁切的。</t>
+          <t>亲，我们面料的幅宽是固定不变的哦，店铺不支持自选宽度、也不支持修改宽度呢，没办法按您的要求改宽度，抱歉抱歉～</t>
         </is>
       </c>
     </row>

--- a/customer_service_import_template.xlsx
+++ b/customer_service_import_template.xlsx
@@ -1,48 +1,155 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ai客服\Customer-Agent-main\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5982B336-92BA-4B3E-B4A9-E58E2FD053EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="1584" yWindow="1584" windowWidth="23040" windowHeight="12120" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="1584" yWindow="1584" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="客服知识" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="客服知识" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="32">
+  <si>
+    <t>一级分类</t>
+  </si>
+  <si>
+    <t>二级分类</t>
+  </si>
+  <si>
+    <t>话术标题</t>
+  </si>
+  <si>
+    <t>话术内容</t>
+  </si>
+  <si>
+    <t>物流</t>
+  </si>
+  <si>
+    <t>发货</t>
+  </si>
+  <si>
+    <t>发货时间</t>
+  </si>
+  <si>
+    <t>亲，非预售款一般成团后24小时内发出，最迟不超过48小时。</t>
+  </si>
+  <si>
+    <t>售后</t>
+  </si>
+  <si>
+    <t>退换货</t>
+  </si>
+  <si>
+    <t>退换货政策</t>
+  </si>
+  <si>
+    <t>本店均为剪裁面料类商品，均不支持7天无理由退换货（面料一经剪裁影响二次销售）。仅接受质量问题、错发或漏发的退换，需提供清晰照片凭证并在签收后48小时内联系客服处理。</t>
+  </si>
+  <si>
+    <t>快递</t>
+  </si>
+  <si>
+    <t>查物流</t>
+  </si>
+  <si>
+    <t>您的订单物流我们会实时跟进，发货后可在拼多多App「我的订单」查看物流轨迹。</t>
+  </si>
+  <si>
+    <t>支付</t>
+  </si>
+  <si>
+    <t>优惠券</t>
+  </si>
+  <si>
+    <t>店铺优惠券在结算时自动抵扣，具体以商品详情页说明为准。</t>
+  </si>
+  <si>
+    <t>服务</t>
+  </si>
+  <si>
+    <t>裁剪</t>
+  </si>
+  <si>
+    <t>按米裁剪</t>
+  </si>
+  <si>
+    <t>亲，本店面料支持按米裁剪哦。您下单时在订单备注里写清楚需要的米数即可（例如"裁2.5米"）。默认多拍连裁：您拍几件我们就把布料连成整段一起裁切，保证是一整段。如果对长度有特殊要求也可以在备注里说明哦。</t>
+  </si>
+  <si>
+    <t>无赠送活动</t>
+  </si>
+  <si>
+    <t>亲，本店目前没有任何赠送或优惠活动哦。不管买多少米都不送，没有买几送几、满减、折扣之类的促销。价格就是商品标价，按实际购买数量计费，不搞任何套路。</t>
+  </si>
+  <si>
+    <t>质量</t>
+  </si>
+  <si>
+    <t>裁剪(剪裁)质量</t>
+  </si>
+  <si>
+    <t>亲，本店裁剪（也常写剪裁）质量您放心哦。每米面料出厂前都经过验布和质检，裁切边缘平整、不毛边、尺寸精准，按您备注的米数连成整段一起裁。如果您收到的裁剪质量不满意（如毛边、尺寸偏差），拍清晰照片联系客服，我们核实后给您处理或补发。</t>
+  </si>
+  <si>
+    <t>规格</t>
+  </si>
+  <si>
+    <t>面料宽度/幅宽</t>
+  </si>
+  <si>
+    <t>亲，我们面料的幅宽是1.41~1.45米之间哦。不同批次可能会有一点点浮动，但基本都在这个范围呢。</t>
+  </si>
+  <si>
+    <t>宽度能否修改/自选</t>
+  </si>
+  <si>
+    <t>亲，我们面料的幅宽是固定不变的哦，店铺不支持自选宽度、也不支持修改宽度呢，没办法按您的要求改宽度呢。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
-      <family val="3"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="11"/>
     </font>
     <font>
+      <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
-      <family val="3"/>
-      <sz val="9"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -66,86 +173,27 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -433,230 +481,151 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
+    <col min="1" max="2" width="14" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="4" max="4" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>一级分类</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>二级分类</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>话术标题</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>话术内容</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>物流</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>发货</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>发货时间</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>亲，非预售款一般成团后24小时内发出，最迟不超过48小时。</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="43.2" customHeight="1">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>售后</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>退换货</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>退换货政策</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>本店均为剪裁面料类商品，均不支持7天无理由退换货（面料一经剪裁影响二次销售）。仅接受质量问题、错发或漏发的退换，需提供清晰照片凭证并在签收后48小时内联系客服处理。</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="28.8" customHeight="1">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>物流</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>快递</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>查物流</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>您的订单物流我们会实时跟进，发货后可在拼多多App「我的订单」查看物流轨迹。</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>支付</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>优惠券</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>店铺优惠券在结算时自动抵扣，具体以商品详情页说明为准。</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>服务</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>裁剪</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>按米裁剪</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>亲，本店面料支持按米裁剪哦。您下单时在订单备注里写清楚需要的米数即可（例如"裁2.5米"）。默认多拍连裁：您拍几件我们就把布料连成整段一起裁切，保证是一整段。如果对长度有特殊要求也可以在备注里说明哦。</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>售后</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>无赠送活动</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>亲，本店目前没有任何赠送或优惠活动哦。不管买多少米都不送，没有买几送几、满减、折扣之类的促销。价格就是商品标价，按实际购买数量计费，不搞任何套路。</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>服务</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>质量</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>裁剪(剪裁)质量</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>亲，本店裁剪（也常写剪裁）质量您放心哦。每米面料出厂前都经过验布和质检，裁切边缘平整、不毛边、尺寸精准，按您备注的米数连成整段一起裁。如果您收到的裁剪质量不满意（如毛边、尺寸偏差），拍清晰照片联系客服，我们核实后给您处理或补发。</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>服务</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>规格</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>面料宽度/幅宽</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>亲，我们面料的幅宽是1.41~1.45米之间哦。不同批次可能会有一点点浮动，但基本都在这个范围呢。</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>服务</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>规格</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>宽度能否修改/自选</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>亲，我们面料的幅宽是固定不变的哦，店铺不支持自选宽度、也不支持修改宽度呢，没办法按您的要求改宽度，抱歉抱歉～</t>
-        </is>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="43.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="28.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" t="s">
+        <v>28</v>
+      </c>
+      <c r="D9" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" t="s">
+        <v>30</v>
+      </c>
+      <c r="D10" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/customer_service_import_template.xlsx
+++ b/customer_service_import_template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ai客服\Customer-Agent-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5982B336-92BA-4B3E-B4A9-E58E2FD053EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC48A0A2-4207-4F61-BA3A-731D98776D90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1584" yWindow="1584" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="客服知识" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="34">
   <si>
     <t>一级分类</t>
   </si>
@@ -85,9 +85,6 @@
     <t>按米裁剪</t>
   </si>
   <si>
-    <t>亲，本店面料支持按米裁剪哦。您下单时在订单备注里写清楚需要的米数即可（例如"裁2.5米"）。默认多拍连裁：您拍几件我们就把布料连成整段一起裁切，保证是一整段。如果对长度有特殊要求也可以在备注里说明哦。</t>
-  </si>
-  <si>
     <t>无赠送活动</t>
   </si>
   <si>
@@ -116,14 +113,29 @@
   </si>
   <si>
     <t>亲，我们面料的幅宽是固定不变的哦，店铺不支持自选宽度、也不支持修改宽度呢，没办法按您的要求改宽度呢。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>特殊尺寸/小数米</t>
+  </si>
+  <si>
+    <t>亲，本店面料不卖特殊尺寸，只按商品规格售卖。
+• 普通花型只售整米（1米、2米、3米及倍数），不卖1.5米、2.5米等小数米。
+• 只有花型名称含「贡缎」且幅宽1.5米的花型，才支持0.5米递增（如2.5米、3.5米），其他小数米同样不卖。
+• 规格里有1.5米就可以买1.5米；规格里没有的小数米，请按最接近的整米规格下单。</t>
+  </si>
+  <si>
+    <t>亲，本店面料按商品规格售卖，规格上有的米数才能下单，规格没有的长度不卖。
+普通花型（幅宽1.41~1.45米）只售整米：1米、2米、3米……即规格的整米倍数。
+花型名称含「贡缎」且幅宽1.5米的花型，可售0.5米递增：2.5米、3.5米、4.5米等，但其他小数米（如1.2米、2.3米）仍不卖。
+多拍连裁：您拍几件，我们就把该规格的长度连成整段一起裁切。例如规格是2米，您拍2件就是4米一整段。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -140,6 +152,13 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="9"/>
       <name val="宋体"/>
       <family val="3"/>
@@ -147,7 +166,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -159,8 +178,18 @@
         <fgColor rgb="FF4472C4"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left/>
       <right/>
@@ -170,14 +199,17 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+  <cellXfs count="4">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -185,7 +217,7 @@
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -482,12 +514,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="14" customWidth="1"/>
-    <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="60" customWidth="1"/>
+    <col min="1" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="4" max="4" width="80" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -505,127 +537,141 @@
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="43.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="A3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="3" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="28.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="A4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="3" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="A5" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="3" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+    <row r="6" spans="1:4" ht="86.4" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" t="s">
+      <c r="D7" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D7" t="s">
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+      <c r="C8" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B8" t="s">
-        <v>24</v>
-      </c>
-      <c r="C8" t="s">
-        <v>25</v>
-      </c>
-      <c r="D8" t="s">
+      <c r="B9" s="2" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="C9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B9" t="s">
-        <v>27</v>
-      </c>
-      <c r="C9" t="s">
-        <v>28</v>
-      </c>
-      <c r="D9" t="s">
+      <c r="B10" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="D10" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="72" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B10" t="s">
-        <v>27</v>
-      </c>
-      <c r="C10" t="s">
-        <v>30</v>
-      </c>
-      <c r="D10" t="s">
+      <c r="B11" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>31</v>
       </c>
+      <c r="D11" s="3" t="s">
+        <v>32</v>
+      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/customer_service_import_template.xlsx
+++ b/customer_service_import_template.xlsx
@@ -1,174 +1,55 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ai客服\Customer-Agent-main\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC48A0A2-4207-4F61-BA3A-731D98776D90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="客服知识" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="客服知识" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="34">
-  <si>
-    <t>一级分类</t>
-  </si>
-  <si>
-    <t>二级分类</t>
-  </si>
-  <si>
-    <t>话术标题</t>
-  </si>
-  <si>
-    <t>话术内容</t>
-  </si>
-  <si>
-    <t>物流</t>
-  </si>
-  <si>
-    <t>发货</t>
-  </si>
-  <si>
-    <t>发货时间</t>
-  </si>
-  <si>
-    <t>亲，非预售款一般成团后24小时内发出，最迟不超过48小时。</t>
-  </si>
-  <si>
-    <t>售后</t>
-  </si>
-  <si>
-    <t>退换货</t>
-  </si>
-  <si>
-    <t>退换货政策</t>
-  </si>
-  <si>
-    <t>本店均为剪裁面料类商品，均不支持7天无理由退换货（面料一经剪裁影响二次销售）。仅接受质量问题、错发或漏发的退换，需提供清晰照片凭证并在签收后48小时内联系客服处理。</t>
-  </si>
-  <si>
-    <t>快递</t>
-  </si>
-  <si>
-    <t>查物流</t>
-  </si>
-  <si>
-    <t>您的订单物流我们会实时跟进，发货后可在拼多多App「我的订单」查看物流轨迹。</t>
-  </si>
-  <si>
-    <t>支付</t>
-  </si>
-  <si>
-    <t>优惠券</t>
-  </si>
-  <si>
-    <t>店铺优惠券在结算时自动抵扣，具体以商品详情页说明为准。</t>
-  </si>
-  <si>
-    <t>服务</t>
-  </si>
-  <si>
-    <t>裁剪</t>
-  </si>
-  <si>
-    <t>按米裁剪</t>
-  </si>
-  <si>
-    <t>无赠送活动</t>
-  </si>
-  <si>
-    <t>亲，本店目前没有任何赠送或优惠活动哦。不管买多少米都不送，没有买几送几、满减、折扣之类的促销。价格就是商品标价，按实际购买数量计费，不搞任何套路。</t>
-  </si>
-  <si>
-    <t>质量</t>
-  </si>
-  <si>
-    <t>裁剪(剪裁)质量</t>
-  </si>
-  <si>
-    <t>亲，本店裁剪（也常写剪裁）质量您放心哦。每米面料出厂前都经过验布和质检，裁切边缘平整、不毛边、尺寸精准，按您备注的米数连成整段一起裁。如果您收到的裁剪质量不满意（如毛边、尺寸偏差），拍清晰照片联系客服，我们核实后给您处理或补发。</t>
-  </si>
-  <si>
-    <t>规格</t>
-  </si>
-  <si>
-    <t>面料宽度/幅宽</t>
-  </si>
-  <si>
-    <t>亲，我们面料的幅宽是1.41~1.45米之间哦。不同批次可能会有一点点浮动，但基本都在这个范围呢。</t>
-  </si>
-  <si>
-    <t>宽度能否修改/自选</t>
-  </si>
-  <si>
-    <t>亲，我们面料的幅宽是固定不变的哦，店铺不支持自选宽度、也不支持修改宽度呢，没办法按您的要求改宽度呢。</t>
-  </si>
-  <si>
-    <t>特殊尺寸/小数米</t>
-  </si>
-  <si>
-    <t>亲，本店面料不卖特殊尺寸，只按商品规格售卖。
-• 普通花型只售整米（1米、2米、3米及倍数），不卖1.5米、2.5米等小数米。
-• 只有花型名称含「贡缎」且幅宽1.5米的花型，才支持0.5米递增（如2.5米、3.5米），其他小数米同样不卖。
-• 规格里有1.5米就可以买1.5米；规格里没有的小数米，请按最接近的整米规格下单。</t>
-  </si>
-  <si>
-    <t>亲，本店面料按商品规格售卖，规格上有的米数才能下单，规格没有的长度不卖。
-普通花型（幅宽1.41~1.45米）只售整米：1米、2米、3米……即规格的整米倍数。
-花型名称含「贡缎」且幅宽1.5米的花型，可售0.5米递增：2.5米、3.5米、4.5米等，但其他小数米（如1.2米、2.3米）仍不卖。
-多拍连裁：您拍几件，我们就把该规格的长度连成整段一起裁切。例如规格是2米，您拍2件就是4米一整段。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="4">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <family val="3"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <family val="3"/>
       <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -179,7 +60,7 @@
       </patternFill>
     </fill>
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
   </fills>
   <borders count="2">
@@ -199,33 +80,93 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+  <cellXfs count="5">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -513,165 +454,258 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="20" customWidth="1"/>
-    <col min="4" max="4" width="80" customWidth="1"/>
+    <col width="12" customWidth="1" style="4" min="1" max="2"/>
+    <col width="20" customWidth="1" style="4" min="3" max="3"/>
+    <col width="80" customWidth="1" style="4" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="43.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="28.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="86.4" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="72" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>32</v>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>一级分类</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>二级分类</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>话术标题</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>话术内容</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>物流</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>发货</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>发货时间</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>亲，非预售款一般成团后24小时内发出，最迟不超过48小时。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="43.2" customHeight="1" s="4">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>售后</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>退换货</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>退换货政策</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>本店均为剪裁面料类商品，均不支持7天无理由退换货（面料一经剪裁影响二次销售）。仅接受质量问题、错发或漏发的退换，需提供清晰照片凭证并在签收后48小时内联系客服处理。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="28.8" customHeight="1" s="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>物流</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>快递</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>查物流</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>您的订单物流我们会实时跟进，发货后可在拼多多App「我的订单」查看物流轨迹。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>支付</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>优惠券</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>店铺优惠券在结算时自动抵扣，具体以商品详情页说明为准。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="86.40000000000001" customHeight="1" s="4">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>服务</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>裁剪</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>按米裁剪</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>亲，本店面料按商品规格售卖，规格上有的米数才能下单，规格没有的长度不卖。
+普通花型（幅宽1.41~1.45米）只售整米：1米、2米、3米……即规格的整米倍数。
+花型名称含「贡缎」且幅宽1.5米的花型，可售0.5米递增：2.5米、3.5米、4.5米等，但其他小数米（如1.2米、2.3米）仍不卖。
+多拍连裁：您拍几件，我们就把该规格的长度连成整段一起裁切。例如规格是2米，您拍2件就是4米一整段。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>售后</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>无赠送活动</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>亲，本店目前没有任何赠送或优惠活动哦。不管买多少米都不送，没有买几送几、满减、折扣之类的促销。价格就是商品标价，按实际购买数量计费，不搞任何套路。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>服务</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>质量</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>裁剪(剪裁)质量</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>亲，本店裁剪（也常写剪裁）质量您放心哦。每米面料出厂前都经过验布和质检，裁切边缘平整、不毛边、尺寸精准，多拍的件数会按订单规格米数连成整段一起裁。如果您收到的裁剪质量不满意（如毛边、尺寸偏差），拍清晰照片联系客服，我们核实后给您处理或补发。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>服务</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>规格</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>面料宽度/幅宽</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>亲，我们面料的幅宽是1.41~1.45米之间哦。不同批次可能会有一点点浮动，但基本都在这个范围呢。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>服务</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>规格</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>宽度能否修改/自选</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>亲，我们面料的幅宽是固定不变的哦，店铺不支持自选宽度、也不支持修改宽度呢，没办法按您的要求改宽度呢。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="72" customHeight="1" s="4">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>服务</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>裁剪</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>特殊尺寸/小数米</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>亲，本店面料不卖特殊尺寸，只按商品规格售卖。
+• 普通花型只售整米（1米、2米、3米及倍数），不卖1.5米、2.5米等小数米。
+• 只有花型名称含「贡缎」且幅宽1.5米的花型，才支持0.5米递增（如2.5米、3.5米），其他小数米同样不卖。
+• 规格里有1.5米就可以买1.5米；规格里没有的小数米，请按最接近的整米规格下单。</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/customer_service_import_template.xlsx
+++ b/customer_service_import_template.xlsx
@@ -592,7 +592,7 @@
         <is>
           <t>亲，本店面料按商品规格售卖，规格上有的米数才能下单，规格没有的长度不卖。
 普通花型（幅宽1.41~1.45米）只售整米：1米、2米、3米……即规格的整米倍数。
-花型名称含「贡缎」且幅宽1.5米的花型，可售0.5米递增：2.5米、3.5米、4.5米等，但其他小数米（如1.2米、2.3米）仍不卖。
+贡缎类花型（花型名称含「贡缎」且幅宽1.5米）：支持0.5米递增，1.5米、2.5米、3.5米等，规格里有的都能下单。
 多拍连裁：您拍几件，我们就把该规格的长度连成整段一起裁切。例如规格是2米，您拍2件就是4米一整段。</t>
         </is>
       </c>
@@ -699,9 +699,9 @@
       <c r="D11" s="3" t="inlineStr">
         <is>
           <t>亲，本店面料不卖特殊尺寸，只按商品规格售卖。
-• 普通花型只售整米（1米、2米、3米及倍数），不卖1.5米、2.5米等小数米。
-• 只有花型名称含「贡缎」且幅宽1.5米的花型，才支持0.5米递增（如2.5米、3.5米），其他小数米同样不卖。
-• 规格里有1.5米就可以买1.5米；规格里没有的小数米，请按最接近的整米规格下单。</t>
+• 先看买家当前咨询的商品：花型名称含「贡缎」且幅宽1.5米 → 该商品支持0.5米递增，1.5米、2.5米、3.5米等规格里有的都能买，直接答复可以买。
+• 普通花型（幅宽1.41~1.45米）只售整米（1米、2米、3米及倍数），不卖小数米。
+• 无论哪种花型，0.5米递增以外的小数米（如1.2米、2.3米）都不卖；规格里没有的长度不卖。</t>
         </is>
       </c>
     </row>

--- a/customer_service_import_template.xlsx
+++ b/customer_service_import_template.xlsx
@@ -590,10 +590,10 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>亲，本店面料按商品规格售卖，规格上有的米数才能下单，规格没有的长度不卖。
-普通花型（幅宽1.41~1.45米）只售整米：1米、2米、3米……即规格的整米倍数。
-贡缎类花型（花型名称含「贡缎」且幅宽1.5米）：支持0.5米递增，1.5米、2.5米、3.5米等，规格里有的都能下单。
-多拍连裁：您拍几件，我们就把该规格的长度连成整段一起裁切。例如规格是2米，您拍2件就是4米一整段。</t>
+          <t>亲，本店面料按商品规格售卖，规格上有的米数才能下单。
+普通花型（幅宽1.41~1.45米）只售整米：1米、2米、3米及倍数，整米可以通过多拍组合实现。例如您要4米就拍2个2米，要5米就拍2米+3米各一件，要6米就拍2个3米或3个2米，我们都会连成整段一起裁切。
+贡缎类花型（花型名称含「贡缎」且幅宽1.5米）：支持0.5米递增，1.5米、2.5米、3.5米等规格里有的都能下单。
+不能卖的是：规格库里无法组合出来的长度、0.5米递增以外的小数米（如1.2米、2.3米）、以及任何要求备注/定制/按需裁剪的特殊长度。</t>
         </is>
       </c>
     </row>
@@ -700,8 +700,8 @@
         <is>
           <t>亲，本店面料不卖特殊尺寸，只按商品规格售卖。
 • 先看买家当前咨询的商品：花型名称含「贡缎」且幅宽1.5米 → 该商品支持0.5米递增，1.5米、2.5米、3.5米等规格里有的都能买，直接答复可以买。
-• 普通花型（幅宽1.41~1.45米）只售整米（1米、2米、3米及倍数），不卖小数米。
-• 无论哪种花型，0.5米递增以外的小数米（如1.2米、2.3米）都不卖；规格里没有的长度不卖。</t>
+• 普通花型（幅宽1.41~1.45米）只售整米：1米、2米、3米及倍数。整米可以通过多拍组合实现，例如4米拍2个2米、5米拍2米+3米、6米拍2个3米或3个2米。不要对整米需求说"不支持""面料长度固定"。
+• 不能卖的是：规格库里无法组合出来的长度、0.5米递增以外的小数米（如1.2米、2.3米）、以及任何要求备注/定制/按需裁剪的特殊长度。</t>
         </is>
       </c>
     </row>

--- a/customer_service_import_template.xlsx
+++ b/customer_service_import_template.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="12" customWidth="1" style="4" min="1" max="2"/>
@@ -705,6 +705,28 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>物流</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>运费险</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>运费险</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>亲，本店商品不带运费险哦。面料是剪裁类商品，不支持无理由退换，所以也没有赠送运费险。如果是质量问题、错发或漏发，您拍清晰照片联系我们核实，运费由我们承担，会给您安排退换或补发，请放心。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
